--- a/data/VPLMN_MVNO_table.xlsx
+++ b/data/VPLMN_MVNO_table.xlsx
@@ -1,20 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Semetch\GNOC_Ticket_Metrices\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AE99F3D-D4CD-4397-9DF2-37EE56672C03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$39</definedName>
+  </definedNames>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="109">
   <si>
     <t>TinyId</t>
   </si>
@@ -34,251 +43,320 @@
     <t>Duration</t>
   </si>
   <si>
-    <t>2026-07-06 05:44:25 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-10 22:28:03 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-09 07:04:26 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-10 05:27:58 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-04 11:24:25 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-08 23:27:59 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-08 22:46:44 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-06 16:24:27 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-07 12:04:23 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-06 08:44:25 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-08 22:06:46 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-09 05:04:25 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-08 10:44:27 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-09 02:24:27 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-09 01:44:27 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-10 07:47:56 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-10 01:24:24 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-04 21:47:49 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-10 01:44:25 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-07 21:47:54 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-09 13:48:07 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-07 14:26:43 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-06 04:07:51 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-06 21:04:24 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-06 12:04:26 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-07 22:24:26 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-10 05:24:27 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-08 22:04:25 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-08 22:44:26 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-08 08:24:26 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-07 13:24:25 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-10 06:04:21 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-10 17:44:24 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-07 00:26:41 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-09 04:24:26 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-08 09:47:54 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-09 20:44:20 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-09 00:26:45 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-08 23:44:25 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-08 23:26:41 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-08 21:44:20 UTC</t>
-  </si>
-  <si>
-    <t>Hi3G Access AB</t>
+    <t>2026-07-16 11:24:25 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-16 11:07:54 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-16 06:46:44 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-16 07:04:34 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-17 22:24:24 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-15 14:44:25 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-16 11:28:04 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-14 21:26:37 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-11 18:06:46 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-14 11:47:55 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-15 00:46:45 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-17 22:44:23 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-14 08:44:23 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-14 21:28:07 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-15 10:04:29 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-11 13:04:24 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-14 21:24:20 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-17 02:44:25 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-13 22:24:26 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-15 09:44:29 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-16 02:44:24 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-14 00:24:25 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-13 10:04:24 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-15 07:24:28 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-15 22:04:23 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-17 09:07:55 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-15 00:44:29 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-15 07:26:39 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-14 01:04:24 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-17 10:04:37 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-16 09:24:23 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-15 12:44:23 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-12 14:24:27 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-15 13:24:31 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-17 13:44:26 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-16 21:24:26 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-17 07:04:21 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-17 06:47:05 UTC</t>
+  </si>
+  <si>
+    <t>Bouygues Telecom</t>
   </si>
   <si>
     <t>Telekom Deutschland GmbH (T-Mobile)</t>
   </si>
   <si>
-    <t>Emirates Integrated Telecommunications Company PJSC</t>
-  </si>
-  <si>
-    <t>Telefónica Germany GmbH &amp; Co. oHG</t>
+    <t>Telcel - América Móvil</t>
+  </si>
+  <si>
+    <t>Turkcell Iletisim Hizmetleri A.S.</t>
+  </si>
+  <si>
+    <t>Vodafone Portugal - Comunicações Pessoais, S.A.</t>
+  </si>
+  <si>
+    <t>Vodafone Ireland Limited</t>
+  </si>
+  <si>
+    <t>AT&amp;T Mobility</t>
+  </si>
+  <si>
+    <t>Videotron Ltd.</t>
+  </si>
+  <si>
+    <t>KT Corporation</t>
+  </si>
+  <si>
+    <t>KPN B.V.</t>
+  </si>
+  <si>
+    <t>Sierra Wireless Sweden</t>
+  </si>
+  <si>
+    <t>Hutchison 3G UK Limited</t>
+  </si>
+  <si>
+    <t>Vodafone D2 GmbH</t>
+  </si>
+  <si>
+    <t>Orange France</t>
+  </si>
+  <si>
+    <t>MTN - Mobile Telephone Networks (Pty) Ltd.</t>
+  </si>
+  <si>
+    <t>A1 Telekom Austria AG</t>
+  </si>
+  <si>
+    <t>Telecom Italia SpA</t>
   </si>
   <si>
     <t>Wind Tre S.p.A.</t>
   </si>
   <si>
-    <t>Salt Mobile SA</t>
-  </si>
-  <si>
-    <t>AT&amp;T Mobility</t>
-  </si>
-  <si>
-    <t>Vodafone Ltd</t>
-  </si>
-  <si>
-    <t>A1 Telekom Austria AG</t>
-  </si>
-  <si>
-    <t>Wataniya Télécom Algérie (Ooredo)</t>
-  </si>
-  <si>
-    <t>Latvijas Mobilais Telefons</t>
-  </si>
-  <si>
-    <t>Orange France</t>
-  </si>
-  <si>
-    <t>Wind Tre S.p.A</t>
-  </si>
-  <si>
-    <t>Rogers Wireless</t>
-  </si>
-  <si>
-    <t>Proximus Luxembourg S.A</t>
-  </si>
-  <si>
-    <t>Sunrise Communications AG</t>
-  </si>
-  <si>
-    <t>Vodafone Hungary Mobile Telecommunications Company Limited</t>
-  </si>
-  <si>
-    <t>Société Réunionnaise du Radiotéléphone</t>
-  </si>
-  <si>
-    <t>Telstra Corporation Limited</t>
-  </si>
-  <si>
-    <t>Telia Norge</t>
-  </si>
-  <si>
-    <t>Société Réunionnaise du R</t>
-  </si>
-  <si>
-    <t>Taiwan Mobile Co.Ltd</t>
-  </si>
-  <si>
-    <t>Telia Nattjanster Norden AB</t>
+    <t>Telefónica Móviles España S.A.</t>
+  </si>
+  <si>
+    <t>Vodafone España, S.A.U.</t>
+  </si>
+  <si>
+    <t>Bell Mobility Inc.</t>
+  </si>
+  <si>
+    <t>Bharti Airtel Limited</t>
+  </si>
+  <si>
+    <t>Orange Burkina Faso</t>
+  </si>
+  <si>
+    <t>Bell Mobility Inc</t>
+  </si>
+  <si>
+    <t>Telus Communications Inc.</t>
+  </si>
+  <si>
+    <t>Scancom Limited</t>
+  </si>
+  <si>
+    <t>MTN - Mobile Telephone</t>
+  </si>
+  <si>
+    <t>Post Luxembourg</t>
+  </si>
+  <si>
+    <t>Maxis Broadband Sdn. Bhd.</t>
+  </si>
+  <si>
+    <t>Airtel Networks Ltd Nigeria</t>
+  </si>
+  <si>
+    <t>France</t>
+  </si>
+  <si>
+    <t>Germany</t>
+  </si>
+  <si>
+    <t>Mexico</t>
+  </si>
+  <si>
+    <t>Turkey</t>
+  </si>
+  <si>
+    <t>Portugal</t>
+  </si>
+  <si>
+    <t>Ireland</t>
+  </si>
+  <si>
+    <t>United States of America</t>
+  </si>
+  <si>
+    <t>Canada</t>
+  </si>
+  <si>
+    <t>South Korea</t>
+  </si>
+  <si>
+    <t>Netherlands</t>
+  </si>
+  <si>
+    <t>Sweden</t>
+  </si>
+  <si>
+    <t>China</t>
+  </si>
+  <si>
+    <t>South Africa</t>
+  </si>
+  <si>
+    <t>Austria</t>
+  </si>
+  <si>
+    <t>Italy</t>
+  </si>
+  <si>
+    <t>Spain</t>
+  </si>
+  <si>
+    <t>Gujarat</t>
+  </si>
+  <si>
+    <t>Ghana</t>
+  </si>
+  <si>
+    <t>Luxembourg</t>
+  </si>
+  <si>
+    <t>Malaysia</t>
+  </si>
+  <si>
+    <t>Nigeria</t>
+  </si>
+  <si>
+    <t>BICS</t>
   </si>
   <si>
     <t>MBQT</t>
   </si>
   <si>
+    <t>SPARKLE</t>
+  </si>
+  <si>
+    <t>SPARKLE, JT</t>
+  </si>
+  <si>
+    <t>ORANGE_901,</t>
+  </si>
+  <si>
+    <t>MBQT,JT,Orange_901</t>
+  </si>
+  <si>
+    <t>Sparkle</t>
+  </si>
+  <si>
+    <t>JT, SPARKLE</t>
+  </si>
+  <si>
+    <t>Orange_901</t>
+  </si>
+  <si>
+    <t>Sparkle/BICS/Orange_901</t>
+  </si>
+  <si>
+    <t>JT, ORANGE_901</t>
+  </si>
+  <si>
+    <t>ORANGE_901</t>
+  </si>
+  <si>
     <t>JT</t>
   </si>
   <si>
-    <t>Orange_901</t>
-  </si>
-  <si>
-    <t>Orange , BICS</t>
-  </si>
-  <si>
-    <t>SPARKLE</t>
-  </si>
-  <si>
-    <t>Orange_901,BICS,JT</t>
-  </si>
-  <si>
-    <t>BICS</t>
-  </si>
-  <si>
-    <t>SPARKLE, Orange_901</t>
-  </si>
-  <si>
-    <t>Orange901</t>
-  </si>
-  <si>
-    <t>Sparkle</t>
-  </si>
-  <si>
-    <t>PCCW</t>
-  </si>
-  <si>
-    <t>JT &amp; Orange_901</t>
-  </si>
-  <si>
-    <t>JT,Orange_901</t>
-  </si>
-  <si>
-    <t>Sparkle, BICS</t>
-  </si>
-  <si>
-    <t>Orange_901,JT,BICS etc.</t>
-  </si>
-  <si>
-    <t>BICS,SPARKLE,JT</t>
+    <t>Orange</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -315,13 +393,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -359,7 +445,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -393,6 +479,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -427,9 +514,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -602,11 +690,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F42"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F39"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="3" max="3" width="26.36328125" customWidth="1"/>
+    <col min="4" max="4" width="22.6328125" customWidth="1"/>
+    <col min="5" max="5" width="25.1796875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -626,281 +719,329 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2">
-        <v>9599</v>
+        <v>11386</v>
       </c>
       <c r="B2" t="s">
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>47</v>
+        <v>44</v>
+      </c>
+      <c r="D2" t="s">
+        <v>74</v>
       </c>
       <c r="E2" t="s">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="F2">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3">
-        <v>10696</v>
+        <v>11382</v>
       </c>
       <c r="B3" t="s">
         <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>48</v>
+        <v>45</v>
+      </c>
+      <c r="D3" t="s">
+        <v>75</v>
       </c>
       <c r="E3" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="F3">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4">
-        <v>10330</v>
+        <v>11374</v>
       </c>
       <c r="B4" t="s">
         <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>49</v>
+        <v>46</v>
+      </c>
+      <c r="D4" t="s">
+        <v>76</v>
       </c>
       <c r="E4" t="s">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="F4">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5">
-        <v>10504</v>
+        <v>11375</v>
       </c>
       <c r="B5" t="s">
         <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>50</v>
+        <v>46</v>
+      </c>
+      <c r="D5" t="s">
+        <v>76</v>
       </c>
       <c r="E5" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="F5">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6">
-        <v>9484</v>
+        <v>11505</v>
       </c>
       <c r="B6" t="s">
         <v>10</v>
       </c>
       <c r="C6" t="s">
-        <v>51</v>
+        <v>47</v>
+      </c>
+      <c r="D6" t="s">
+        <v>77</v>
       </c>
       <c r="E6" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="F6">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7">
-        <v>10254</v>
+        <v>11274</v>
       </c>
       <c r="B7" t="s">
         <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>52</v>
+        <v>48</v>
+      </c>
+      <c r="D7" t="s">
+        <v>78</v>
       </c>
       <c r="E7" t="s">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="F7">
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8">
-        <v>10247</v>
+        <v>11387</v>
       </c>
       <c r="B8" t="s">
         <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>53</v>
+        <v>49</v>
+      </c>
+      <c r="D8" t="s">
+        <v>79</v>
       </c>
       <c r="E8" t="s">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="F8">
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9">
-        <v>9648</v>
+        <v>11218</v>
       </c>
       <c r="B9" t="s">
         <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>51</v>
+        <v>50</v>
+      </c>
+      <c r="D9" t="s">
+        <v>80</v>
       </c>
       <c r="E9" t="s">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="F9">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10">
-        <v>9834</v>
+        <v>10799</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>54</v>
+        <v>51</v>
+      </c>
+      <c r="D10" t="s">
+        <v>81</v>
       </c>
       <c r="E10" t="s">
-        <v>75</v>
+        <v>102</v>
       </c>
       <c r="F10">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11">
-        <v>9619</v>
+        <v>11167</v>
       </c>
       <c r="B11" t="s">
         <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>47</v>
+        <v>52</v>
+      </c>
+      <c r="D11" t="s">
+        <v>82</v>
       </c>
       <c r="E11" t="s">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="F11">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12">
-        <v>10242</v>
+        <v>11234</v>
       </c>
       <c r="B12" t="s">
         <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>53</v>
+        <v>50</v>
+      </c>
+      <c r="D12" t="s">
+        <v>80</v>
       </c>
       <c r="E12" t="s">
-        <v>74</v>
+        <v>101</v>
       </c>
       <c r="F12">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13">
-        <v>10325</v>
+        <v>11506</v>
       </c>
       <c r="B13" t="s">
         <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>55</v>
+        <v>47</v>
+      </c>
+      <c r="D13" t="s">
+        <v>77</v>
       </c>
       <c r="E13" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="F13">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14">
-        <v>10167</v>
+        <v>11163</v>
       </c>
       <c r="B14" t="s">
         <v>18</v>
       </c>
       <c r="C14" t="s">
-        <v>51</v>
+        <v>53</v>
+      </c>
+      <c r="D14" t="s">
+        <v>83</v>
       </c>
       <c r="E14" t="s">
-        <v>72</v>
+        <v>103</v>
       </c>
       <c r="F14">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15">
-        <v>10310</v>
+        <v>11219</v>
       </c>
       <c r="B15" t="s">
         <v>19</v>
       </c>
       <c r="C15" t="s">
-        <v>49</v>
+        <v>54</v>
+      </c>
+      <c r="D15" t="s">
+        <v>84</v>
       </c>
       <c r="E15" t="s">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="F15">
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16">
-        <v>10298</v>
+        <v>11263</v>
       </c>
       <c r="B16" t="s">
         <v>20</v>
       </c>
       <c r="C16" t="s">
-        <v>56</v>
+        <v>55</v>
+      </c>
+      <c r="D16" t="s">
+        <v>85</v>
       </c>
       <c r="E16" t="s">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="F16">
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17">
-        <v>10520</v>
+        <v>10777</v>
       </c>
       <c r="B17" t="s">
         <v>21</v>
       </c>
       <c r="C17" t="s">
-        <v>48</v>
+        <v>56</v>
+      </c>
+      <c r="D17" t="s">
+        <v>75</v>
       </c>
       <c r="E17" t="s">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="F17">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18">
-        <v>10479</v>
+        <v>11217</v>
       </c>
       <c r="B18" t="s">
         <v>22</v>
@@ -908,16 +1049,19 @@
       <c r="C18" t="s">
         <v>57</v>
       </c>
+      <c r="D18" t="s">
+        <v>74</v>
+      </c>
       <c r="E18" t="s">
-        <v>78</v>
+        <v>104</v>
       </c>
       <c r="F18">
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19">
-        <v>9510</v>
+        <v>11444</v>
       </c>
       <c r="B19" t="s">
         <v>23</v>
@@ -925,369 +1069,394 @@
       <c r="C19" t="s">
         <v>58</v>
       </c>
+      <c r="D19" t="s">
+        <v>86</v>
+      </c>
       <c r="E19" t="s">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="F19">
         <v>6</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20">
-        <v>10480</v>
+        <v>11035</v>
       </c>
       <c r="B20" t="s">
         <v>24</v>
       </c>
       <c r="C20" t="s">
-        <v>57</v>
+        <v>59</v>
+      </c>
+      <c r="D20" t="s">
+        <v>87</v>
       </c>
       <c r="E20" t="s">
-        <v>72</v>
+        <v>105</v>
       </c>
       <c r="F20">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21">
-        <v>9962</v>
+        <v>11260</v>
       </c>
       <c r="B21" t="s">
         <v>25</v>
       </c>
       <c r="C21" t="s">
-        <v>58</v>
+        <v>60</v>
+      </c>
+      <c r="D21" t="s">
+        <v>88</v>
       </c>
       <c r="E21" t="s">
-        <v>74</v>
+        <v>106</v>
       </c>
       <c r="F21">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22">
-        <v>10364</v>
+        <v>11360</v>
       </c>
       <c r="B22" t="s">
         <v>26</v>
       </c>
       <c r="C22" t="s">
-        <v>59</v>
+        <v>61</v>
+      </c>
+      <c r="D22" t="s">
+        <v>88</v>
       </c>
       <c r="E22" t="s">
-        <v>80</v>
+        <v>106</v>
       </c>
       <c r="F22">
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23">
-        <v>9853</v>
+        <v>11067</v>
       </c>
       <c r="B23" t="s">
         <v>27</v>
       </c>
       <c r="C23" t="s">
-        <v>60</v>
+        <v>62</v>
+      </c>
+      <c r="D23" t="s">
+        <v>89</v>
       </c>
       <c r="E23" t="s">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="F23">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24">
-        <v>9586</v>
+        <v>10945</v>
       </c>
       <c r="B24" t="s">
         <v>28</v>
       </c>
       <c r="C24" t="s">
-        <v>61</v>
+        <v>63</v>
+      </c>
+      <c r="D24" t="s">
+        <v>89</v>
       </c>
       <c r="E24" t="s">
-        <v>70</v>
+        <v>103</v>
       </c>
       <c r="F24">
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25">
-        <v>9673</v>
+        <v>11250</v>
       </c>
       <c r="B25" t="s">
         <v>29</v>
       </c>
       <c r="C25" t="s">
-        <v>62</v>
+        <v>64</v>
+      </c>
+      <c r="D25" t="s">
+        <v>81</v>
       </c>
       <c r="E25" t="s">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="F25">
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26">
-        <v>9632</v>
+        <v>11323</v>
       </c>
       <c r="B26" t="s">
         <v>30</v>
       </c>
       <c r="C26" t="s">
-        <v>62</v>
+        <v>65</v>
+      </c>
+      <c r="D26" t="s">
+        <v>90</v>
       </c>
       <c r="E26" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="F26">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27">
-        <v>9969</v>
+        <v>11469</v>
       </c>
       <c r="B27" t="s">
         <v>31</v>
       </c>
       <c r="C27" t="s">
-        <v>63</v>
+        <v>66</v>
+      </c>
+      <c r="D27" t="s">
+        <v>74</v>
       </c>
       <c r="E27" t="s">
-        <v>72</v>
+        <v>107</v>
       </c>
       <c r="F27">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28">
-        <v>10502</v>
+        <v>11233</v>
       </c>
       <c r="B28" t="s">
         <v>32</v>
       </c>
       <c r="C28" t="s">
-        <v>64</v>
+        <v>67</v>
+      </c>
+      <c r="D28" t="s">
+        <v>81</v>
       </c>
       <c r="E28" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="F28">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29">
-        <v>10241</v>
+        <v>11251</v>
       </c>
       <c r="B29" t="s">
         <v>33</v>
       </c>
       <c r="C29" t="s">
-        <v>58</v>
+        <v>68</v>
+      </c>
+      <c r="D29" t="s">
+        <v>81</v>
       </c>
       <c r="E29" t="s">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="F29">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30">
-        <v>10246</v>
+        <v>11079</v>
       </c>
       <c r="B30" t="s">
         <v>34</v>
       </c>
       <c r="C30" t="s">
-        <v>58</v>
+        <v>62</v>
+      </c>
+      <c r="D30" t="s">
+        <v>89</v>
       </c>
       <c r="E30" t="s">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="F30">
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31">
-        <v>10149</v>
+        <v>11476</v>
       </c>
       <c r="B31" t="s">
         <v>35</v>
       </c>
       <c r="C31" t="s">
-        <v>65</v>
+        <v>61</v>
+      </c>
+      <c r="D31" t="s">
+        <v>88</v>
       </c>
       <c r="E31" t="s">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="F31">
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:6">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32">
-        <v>9843</v>
+        <v>11377</v>
       </c>
       <c r="B32" t="s">
         <v>36</v>
       </c>
       <c r="C32" t="s">
-        <v>66</v>
+        <v>69</v>
+      </c>
+      <c r="D32" t="s">
+        <v>91</v>
       </c>
       <c r="E32" t="s">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="F32">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33">
-        <v>10510</v>
+        <v>11271</v>
       </c>
       <c r="B33" t="s">
         <v>37</v>
       </c>
       <c r="C33" t="s">
-        <v>67</v>
+        <v>70</v>
+      </c>
+      <c r="D33" t="s">
+        <v>86</v>
       </c>
       <c r="E33" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="F33">
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:6">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34">
-        <v>10541</v>
+        <v>10859</v>
       </c>
       <c r="B34" t="s">
         <v>38</v>
       </c>
       <c r="C34" t="s">
-        <v>62</v>
+        <v>71</v>
+      </c>
+      <c r="D34" t="s">
+        <v>92</v>
       </c>
       <c r="E34" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="F34">
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:6">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35">
-        <v>9711</v>
+        <v>11272</v>
       </c>
       <c r="B35" t="s">
         <v>39</v>
       </c>
       <c r="C35" t="s">
-        <v>60</v>
+        <v>72</v>
+      </c>
+      <c r="D35" t="s">
+        <v>93</v>
       </c>
       <c r="E35" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="F35">
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:6">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36">
-        <v>10322</v>
+        <v>11489</v>
       </c>
       <c r="B36" t="s">
         <v>40</v>
       </c>
       <c r="C36" t="s">
-        <v>51</v>
+        <v>73</v>
+      </c>
+      <c r="D36" t="s">
+        <v>94</v>
       </c>
       <c r="E36" t="s">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="F36">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37">
-        <v>10164</v>
+        <v>11411</v>
       </c>
       <c r="B37" t="s">
         <v>41</v>
       </c>
       <c r="C37" t="s">
-        <v>68</v>
+        <v>47</v>
+      </c>
+      <c r="D37" t="s">
+        <v>77</v>
       </c>
       <c r="E37" t="s">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="F37">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38">
-        <v>10443</v>
+        <v>11463</v>
       </c>
       <c r="B38" t="s">
         <v>42</v>
       </c>
-      <c r="C38" t="s">
-        <v>69</v>
-      </c>
-      <c r="E38" t="s">
-        <v>72</v>
-      </c>
-      <c r="F38">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39">
-        <v>10289</v>
+        <v>11461</v>
       </c>
       <c r="B39" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>10260</v>
-      </c>
-      <c r="B40" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>10253</v>
-      </c>
-      <c r="B41" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>10239</v>
-      </c>
-      <c r="B42" t="s">
-        <v>46</v>
-      </c>
-    </row>
   </sheetData>
+  <autoFilter ref="A1:F39" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>